--- a/artfynd/A 50174-2023 artfynd.xlsx
+++ b/artfynd/A 50174-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126099295</v>
       </c>
       <c r="B2" t="n">
-        <v>58079</v>
+        <v>58080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50174-2023 artfynd.xlsx
+++ b/artfynd/A 50174-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126099295</v>
       </c>
       <c r="B2" t="n">
-        <v>58080</v>
+        <v>58084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50174-2023 artfynd.xlsx
+++ b/artfynd/A 50174-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126099295</v>
       </c>
       <c r="B2" t="n">
-        <v>58084</v>
+        <v>58087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
